--- a/SportsCompUpdater/Sports_Comp.xlsx
+++ b/SportsCompUpdater/Sports_Comp.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/knaaptime/Dropbox/projects/SportsCompUpdater/SportsCompUpdater/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justinlovett/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99995D22-DF39-284E-AB2D-7CD4F72D137E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC43CBF-32BF-D743-9E3F-226C389B0016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{44C9D164-2375-BE43-B3F5-24284E54108D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,33 +24,26 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>LeBron James</t>
-  </si>
-  <si>
-    <t>Luka doncic</t>
-  </si>
-  <si>
-    <t>michael jordan</t>
-  </si>
-  <si>
-    <t>justin lovett</t>
-  </si>
-  <si>
-    <t>jalyen brunson</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Pick</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Starter</t>
   </si>
   <si>
     <t>Points</t>
@@ -71,13 +61,13 @@
     <t>Steals</t>
   </si>
   <si>
-    <t>FT%</t>
+    <t>FT %</t>
   </si>
   <si>
     <t>FG%</t>
   </si>
   <si>
-    <t>3PM</t>
+    <t>3pm</t>
   </si>
   <si>
     <t>FGA</t>
@@ -92,40 +82,344 @@
     <t>FTM</t>
   </si>
   <si>
-    <t>Player</t>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Stephen Curry (G) - GSW</t>
+  </si>
+  <si>
+    <t>Joel Embiid (C) - PHI</t>
+  </si>
+  <si>
+    <t>Devin Booker (G) - PHX</t>
+  </si>
+  <si>
+    <t>Jamal Murray (G) - DEN</t>
+  </si>
+  <si>
+    <t>D'Angelo Russell (G) - BKN</t>
+  </si>
+  <si>
+    <t>Miles Bridges (F) - CHA</t>
+  </si>
+  <si>
+    <t>Mitchell Robinson (C) - NYK</t>
+  </si>
+  <si>
+    <t>Trae Young (G) - ATL</t>
+  </si>
+  <si>
+    <t>Ja Morant (G) - MEM</t>
+  </si>
+  <si>
+    <t>Coby White (G) - CHI</t>
+  </si>
+  <si>
+    <t>Shai Gilgeous-Alexander (G) - OKC</t>
+  </si>
+  <si>
+    <t>Darius Garland (G) - CLE</t>
+  </si>
+  <si>
+    <t>Tyler Herro (G) - MIA</t>
+  </si>
+  <si>
+    <t>Derrick White</t>
+  </si>
+  <si>
+    <t>Deni Avdija</t>
+  </si>
+  <si>
+    <t>Jaylen Brown (F/G) - BOS</t>
+  </si>
+  <si>
+    <t>Aaron Gordon (F) - DEN</t>
+  </si>
+  <si>
+    <t>Draymond Green (F) - GSW</t>
+  </si>
+  <si>
+    <t>Karl-Anthony Towns (C) - MIN</t>
+  </si>
+  <si>
+    <t>Domantas Sabonis (F/C) - SAC</t>
+  </si>
+  <si>
+    <t>Brandon Ingram (F) - NOR</t>
+  </si>
+  <si>
+    <t>Jayson Tatum (F/G) - BOS</t>
+  </si>
+  <si>
+    <t>Bam Adebayo (C/F) - MIA</t>
+  </si>
+  <si>
+    <t>Luka Doncic (G/F) - DAL</t>
+  </si>
+  <si>
+    <t>Anthony Edwards (G) - MIN</t>
+  </si>
+  <si>
+    <t>Jalen Green (G) - HOU</t>
+  </si>
+  <si>
+    <t>Evan Mobley (F/C) - CLE</t>
+  </si>
+  <si>
+    <t>James Harden (G) - PHI</t>
+  </si>
+  <si>
+    <t>Myles Turner (C) - IND</t>
+  </si>
+  <si>
+    <t>Jaren Jackson (F/C) - MEM</t>
+  </si>
+  <si>
+    <t>Michael Porter (F) - DEN</t>
+  </si>
+  <si>
+    <t>Lamelo Ball (G) - CHA</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu (F/C) - ATL</t>
+  </si>
+  <si>
+    <t>Alperen Sengun (C) - HOU</t>
+  </si>
+  <si>
+    <t>Cade Cunningham (G/F) - DET</t>
+  </si>
+  <si>
+    <t>Scottie Barnes (F) - TOR</t>
+  </si>
+  <si>
+    <t>Collin Sexton (G) - UTH</t>
+  </si>
+  <si>
+    <t>Jaden Ivey (G) - DET</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin (G) - IND</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey (G) - PHI</t>
+  </si>
+  <si>
+    <t>Mark Williams (C) - CHA</t>
+  </si>
+  <si>
+    <t>CJ McCollum (G) - NOR</t>
+  </si>
+  <si>
+    <t>Jabari Smith (F) - HOU</t>
+  </si>
+  <si>
+    <t>Chet Holmgren (F) - OKC</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe (G) - POR</t>
+  </si>
+  <si>
+    <t>RJ Barrett - (G/F) - TOR</t>
+  </si>
+  <si>
+    <t>Bradley Beal (G) - PHX</t>
+  </si>
+  <si>
+    <t>Pascal Siakam (F) - IND</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell (G) - CLE</t>
+  </si>
+  <si>
+    <t>Mikal Bridges (F) - BKN</t>
+  </si>
+  <si>
+    <t>Brandon Miller (F) - CHA</t>
+  </si>
+  <si>
+    <t>De'Aaaron Fox (G) - SAS</t>
+  </si>
+  <si>
+    <t>Zach Lavine (G) - SAC</t>
+  </si>
+  <si>
+    <t>Buddy Hield (G) - GSW</t>
+  </si>
+  <si>
+    <t>Jalen Brunson (G) - NYC</t>
+  </si>
+  <si>
+    <t>Amen Thompson (F) - HOU</t>
+  </si>
+  <si>
+    <t>Ausar Thompson (F) - DET</t>
+  </si>
+  <si>
+    <t>Julius Randle (F/C) - MIN</t>
+  </si>
+  <si>
+    <t>Andrew Wiggins (F/G) - MIA</t>
+  </si>
+  <si>
+    <t>Josh Giddey (G/F) - CHI</t>
+  </si>
+  <si>
+    <t>Stephon Castle</t>
+  </si>
+  <si>
+    <t>Donovan Clingan</t>
+  </si>
+  <si>
+    <t>Dereck Lively</t>
+  </si>
+  <si>
+    <t>2025-26</t>
+  </si>
+  <si>
+    <t>Andre Drummond (C) - PHI</t>
+  </si>
+  <si>
+    <t>Cam Thomas</t>
+  </si>
+  <si>
+    <t>Christian Braun</t>
+  </si>
+  <si>
+    <t>Bilal Coulibaly</t>
+  </si>
+  <si>
+    <t>VJ Edgecombe</t>
+  </si>
+  <si>
+    <t>Tre Johnson</t>
+  </si>
+  <si>
+    <t>Jeremiah Fears</t>
+  </si>
+  <si>
+    <t>Jalen Johnson</t>
+  </si>
+  <si>
+    <t>Alex Sarr</t>
+  </si>
+  <si>
+    <t>Dyson Daniels</t>
+  </si>
+  <si>
+    <t>Dylan Harper</t>
+  </si>
+  <si>
+    <t>Ace Bailey</t>
+  </si>
+  <si>
+    <t>Kon Knueppel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFBBBEBF"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Verdana"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="-apple-system"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="-apple-system"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF666666"/>
+        <bgColor rgb="FF666666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F9F9"/>
+        <bgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7B7B7"/>
+        <bgColor rgb="FFB7B7B7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,10 +434,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -161,6 +523,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -172,39 +538,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -256,7 +622,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -367,6 +733,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -375,13 +748,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -446,110 +812,2341 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AB6C8F-06C7-CF43-B855-01E9DA8C9150}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:P109"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.1640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="4.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="12" max="16" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="14">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="13">
+      <c r="A2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+    </row>
+    <row r="3" spans="1:16" ht="14">
+      <c r="A3" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="15">
+        <f>SUM(1336+327)</f>
+        <v>1663</v>
+      </c>
+      <c r="F3" s="16">
+        <f>SUM(270+79)</f>
+        <v>349</v>
+      </c>
+      <c r="G3" s="17">
+        <f>SUM(445+125)</f>
+        <v>570</v>
+      </c>
+      <c r="H3" s="16">
+        <f>SUM(19+9)</f>
+        <v>28</v>
+      </c>
+      <c r="I3" s="17">
+        <f>SUM(89+27)</f>
+        <v>116</v>
+      </c>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="17">
+        <f>SUM(131+30)</f>
+        <v>161</v>
+      </c>
+      <c r="M3" s="17">
+        <f>SUM(1040+302)</f>
+        <v>1342</v>
+      </c>
+      <c r="N3" s="17">
+        <f>SUM(509+125)</f>
+        <v>634</v>
+      </c>
+      <c r="O3" s="17">
+        <f>SUM(246+62)</f>
+        <v>308</v>
+      </c>
+      <c r="P3" s="16">
+        <f>SUM(187+47)</f>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14">
+      <c r="A4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="21">
+        <v>1142</v>
+      </c>
+      <c r="F4" s="16">
+        <v>154</v>
+      </c>
+      <c r="G4" s="16">
+        <v>203</v>
+      </c>
+      <c r="H4" s="16">
+        <v>17</v>
+      </c>
+      <c r="I4" s="16">
+        <v>49</v>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="16">
+        <v>190</v>
+      </c>
+      <c r="M4" s="16">
+        <v>799</v>
+      </c>
+      <c r="N4" s="16">
+        <v>374</v>
+      </c>
+      <c r="O4" s="16">
+        <v>221</v>
+      </c>
+      <c r="P4" s="16">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14">
+      <c r="A5" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="15">
+        <v>748</v>
+      </c>
+      <c r="F5" s="16">
+        <v>108</v>
+      </c>
+      <c r="G5" s="16">
+        <v>89</v>
+      </c>
+      <c r="H5" s="16">
         <v>10</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="I5" s="16">
+        <v>28</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="16">
+        <v>99</v>
+      </c>
+      <c r="M5" s="16">
+        <v>547</v>
+      </c>
+      <c r="N5" s="16">
+        <v>262</v>
+      </c>
+      <c r="O5" s="16">
+        <v>142</v>
+      </c>
+      <c r="P5" s="16">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14">
+      <c r="A6" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="21">
+        <f>SUM(2038+180)</f>
+        <v>2218</v>
+      </c>
+      <c r="F6" s="16">
+        <f>SUM(492+40)</f>
+        <v>532</v>
+      </c>
+      <c r="G6" s="16">
+        <f>SUM(364+23)</f>
+        <v>387</v>
+      </c>
+      <c r="H6" s="16">
+        <f>SUM(27+8)</f>
+        <v>35</v>
+      </c>
+      <c r="I6" s="16">
+        <f>SUM(72+6)</f>
+        <v>78</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="20">
+        <f>SUM(140+17)</f>
+        <v>157</v>
+      </c>
+      <c r="M6" s="16">
+        <f>SUM(1543+143)</f>
+        <v>1686</v>
+      </c>
+      <c r="N6" s="16">
+        <f>SUM(736+65)</f>
+        <v>801</v>
+      </c>
+      <c r="O6" s="16">
+        <f>SUM(536+46)</f>
+        <v>582</v>
+      </c>
+      <c r="P6" s="16">
+        <f>SUM(426+33)</f>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14">
+      <c r="A7" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+    </row>
+    <row r="8" spans="1:16" ht="14">
+      <c r="A8" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+    </row>
+    <row r="9" spans="1:16" ht="14">
+      <c r="A9" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+    </row>
+    <row r="10" spans="1:16" ht="14">
+      <c r="A10" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+    </row>
+    <row r="11" spans="1:16" ht="14">
+      <c r="A11" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+    </row>
+    <row r="12" spans="1:16" ht="14">
+      <c r="A12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+    </row>
+    <row r="13" spans="1:16" ht="14">
+      <c r="A13" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" spans="1:16" ht="14">
+      <c r="A14" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+    </row>
+    <row r="15" spans="1:16" ht="14">
+      <c r="A15" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+    </row>
+    <row r="16" spans="1:16" ht="14">
+      <c r="A16" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+    </row>
+    <row r="17" spans="1:16" ht="14">
+      <c r="A17" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="16"/>
+    </row>
+    <row r="18" spans="1:16" ht="14">
+      <c r="A18" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="16"/>
+    </row>
+    <row r="19" spans="1:16" ht="14">
+      <c r="A19" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+    </row>
+    <row r="20" spans="1:16" ht="14">
+      <c r="A20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="16"/>
+    </row>
+    <row r="21" spans="1:16" ht="14">
+      <c r="A21" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+    </row>
+    <row r="22" spans="1:16" ht="14">
+      <c r="A22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+    </row>
+    <row r="23" spans="1:16" ht="13">
+      <c r="A23" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+    </row>
+    <row r="24" spans="1:16" ht="13">
+      <c r="A24" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+    </row>
+    <row r="25" spans="1:16" ht="13">
+      <c r="A25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+    </row>
+    <row r="26" spans="1:16" ht="13">
+      <c r="A26" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+    </row>
+    <row r="27" spans="1:16" ht="13">
+      <c r="A27" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+    </row>
+    <row r="28" spans="1:16" ht="13">
+      <c r="A28" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+    </row>
+    <row r="29" spans="1:16" ht="13">
+      <c r="A29" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+    </row>
+    <row r="30" spans="1:16" ht="13">
+      <c r="A30" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+    </row>
+    <row r="31" spans="1:16" ht="13">
+      <c r="A31" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+    </row>
+    <row r="32" spans="1:16" ht="13">
+      <c r="A32" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+    </row>
+    <row r="33" spans="1:16" ht="13">
+      <c r="A33" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+    </row>
+    <row r="34" spans="1:16" ht="13">
+      <c r="A34" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+    </row>
+    <row r="35" spans="1:16" ht="13">
+      <c r="A35" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+    </row>
+    <row r="36" spans="1:16" ht="13">
+      <c r="A36" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+    </row>
+    <row r="37" spans="1:16" ht="13">
+      <c r="A37" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+    </row>
+    <row r="38" spans="1:16" ht="13">
+      <c r="A38" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+    </row>
+    <row r="39" spans="1:16" ht="13">
+      <c r="A39" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+    </row>
+    <row r="40" spans="1:16" ht="13">
+      <c r="A40" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26">
+        <v>1169</v>
+      </c>
+      <c r="F40" s="26">
+        <v>300</v>
+      </c>
+      <c r="G40" s="26">
+        <v>279</v>
+      </c>
+      <c r="H40" s="26">
+        <v>30</v>
+      </c>
+      <c r="I40" s="26">
+        <v>97</v>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="26">
+        <v>101</v>
+      </c>
+      <c r="M40" s="26">
+        <v>1006</v>
+      </c>
+      <c r="N40" s="26">
+        <v>437</v>
+      </c>
+      <c r="O40" s="26">
+        <v>246</v>
+      </c>
+      <c r="P40" s="26">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="13">
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+    </row>
+    <row r="42" spans="1:16" ht="13">
+      <c r="A42" s="25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25">
+        <f t="shared" ref="E42:I42" si="0">SUM(E3:E25)</f>
+        <v>5771</v>
+      </c>
+      <c r="F42" s="25">
+        <f t="shared" si="0"/>
+        <v>1143</v>
+      </c>
+      <c r="G42" s="25">
+        <f t="shared" si="0"/>
+        <v>1249</v>
+      </c>
+      <c r="H42" s="25">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="I42" s="25">
+        <f t="shared" si="0"/>
+        <v>271</v>
+      </c>
+      <c r="J42" s="28">
+        <f>SUM(P42/O42)</f>
+        <v>0.81564245810055869</v>
+      </c>
+      <c r="K42" s="29">
+        <f>SUM(N42/M42)</f>
+        <v>0.47347965249199819</v>
+      </c>
+      <c r="L42" s="25">
+        <f t="shared" ref="L42:P42" si="1">SUM(L3:L25)</f>
+        <v>607</v>
+      </c>
+      <c r="M42" s="25">
+        <f t="shared" si="1"/>
+        <v>4374</v>
+      </c>
+      <c r="N42" s="25">
+        <f t="shared" si="1"/>
+        <v>2071</v>
+      </c>
+      <c r="O42" s="25">
+        <f t="shared" si="1"/>
+        <v>1253</v>
+      </c>
+      <c r="P42" s="25">
+        <f t="shared" si="1"/>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="13">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+    </row>
+    <row r="44" spans="1:16" ht="14">
+      <c r="A44" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="17"/>
+    </row>
+    <row r="45" spans="1:16" ht="14">
+      <c r="A45" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="17"/>
+    </row>
+    <row r="46" spans="1:16" ht="14">
+      <c r="A46" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="17"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+    </row>
+    <row r="47" spans="1:16" ht="14">
+      <c r="A47" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="17"/>
+    </row>
+    <row r="48" spans="1:16" ht="14">
+      <c r="A48" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="17"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+    </row>
+    <row r="49" spans="1:16" ht="14">
+      <c r="A49" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="17"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+    </row>
+    <row r="50" spans="1:16" ht="14">
+      <c r="A50" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="17"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+    </row>
+    <row r="51" spans="1:16" ht="14">
+      <c r="A51" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="17"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+    </row>
+    <row r="52" spans="1:16" ht="14">
+      <c r="A52" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+    </row>
+    <row r="53" spans="1:16" ht="14">
+      <c r="A53" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="17"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+    </row>
+    <row r="54" spans="1:16" ht="14">
+      <c r="A54" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="17"/>
+    </row>
+    <row r="55" spans="1:16" ht="14">
+      <c r="A55" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="17"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
+    </row>
+    <row r="56" spans="1:16" ht="14">
+      <c r="A56" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="17"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+    </row>
+    <row r="57" spans="1:16" ht="14">
+      <c r="A57" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
+    </row>
+    <row r="58" spans="1:16" ht="14">
+      <c r="A58" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="17"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+    </row>
+    <row r="59" spans="1:16" ht="14">
+      <c r="A59" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="17"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+    </row>
+    <row r="60" spans="1:16" ht="14">
+      <c r="A60" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+    </row>
+    <row r="61" spans="1:16" ht="14">
+      <c r="A61" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+    </row>
+    <row r="62" spans="1:16" ht="14">
+      <c r="A62" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+    </row>
+    <row r="63" spans="1:16" ht="13">
+      <c r="A63" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="17"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+    </row>
+    <row r="64" spans="1:16" ht="13">
+      <c r="A64" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="17"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+    </row>
+    <row r="65" spans="1:16" ht="13">
+      <c r="A65" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="17"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+    </row>
+    <row r="66" spans="1:16" ht="13">
+      <c r="A66" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="26"/>
+    </row>
+    <row r="67" spans="1:16" ht="13">
+      <c r="A67" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="17"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="26"/>
+    </row>
+    <row r="68" spans="1:16" ht="13">
+      <c r="A68" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="17"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
+    </row>
+    <row r="69" spans="1:16" ht="13">
+      <c r="A69" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="17"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="26"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="26"/>
+    </row>
+    <row r="70" spans="1:16" ht="13">
+      <c r="A70" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+    </row>
+    <row r="71" spans="1:16" ht="13">
+      <c r="A71" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="17"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+    </row>
+    <row r="72" spans="1:16" ht="13">
+      <c r="A72" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="17"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+    </row>
+    <row r="73" spans="1:16" ht="13">
+      <c r="A73" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="17"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+    </row>
+    <row r="74" spans="1:16" ht="13">
+      <c r="A74" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="17"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+    </row>
+    <row r="75" spans="1:16" ht="13">
+      <c r="A75" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="17"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+    </row>
+    <row r="76" spans="1:16" ht="13">
+      <c r="A76" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="17"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+    </row>
+    <row r="77" spans="1:16" ht="13">
+      <c r="A77" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="17"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+    </row>
+    <row r="78" spans="1:16" ht="13">
+      <c r="A78" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="17"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+    </row>
+    <row r="79" spans="1:16" ht="13">
+      <c r="A79" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="17"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
+    </row>
+    <row r="80" spans="1:16" ht="13">
+      <c r="A80" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="17"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+    </row>
+    <row r="81" spans="1:16" ht="13">
+      <c r="A81" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="17"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+    </row>
+    <row r="82" spans="1:16" ht="13">
+      <c r="A82" s="26"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="17"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
+      <c r="N82" s="26"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="26"/>
+    </row>
+    <row r="83" spans="1:16" ht="13">
+      <c r="A83" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5">
+        <f t="shared" ref="E83:I83" si="2">SUM(E44:E68)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F83" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="30" t="e">
+        <f>SUM(P83/O83)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K83" s="31" t="e">
+        <f>SUM(N83/M83)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L83" s="5">
+        <f t="shared" ref="L83:P83" si="3">SUM(L44:L68)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N83" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O83" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P83" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="13">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="9"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+      <c r="N84" s="8"/>
+      <c r="O84" s="8"/>
+      <c r="P84" s="8"/>
+    </row>
+    <row r="85" spans="1:16" ht="13">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+    </row>
+    <row r="86" spans="1:16" ht="13">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5"/>
+    </row>
+    <row r="87" spans="1:16" ht="13">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+    </row>
+    <row r="88" spans="1:16" ht="13">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
+    </row>
+    <row r="89" spans="1:16" ht="13">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="7"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+    </row>
+    <row r="90" spans="1:16" ht="13">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5"/>
+    </row>
+    <row r="91" spans="1:16" ht="13">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+    </row>
+    <row r="92" spans="1:16" ht="13">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+    </row>
+    <row r="93" spans="1:16" ht="13">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+    </row>
+    <row r="94" spans="1:16" ht="13">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5"/>
+    </row>
+    <row r="95" spans="1:16" ht="13">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5"/>
+    </row>
+    <row r="96" spans="1:16" ht="13">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5"/>
+    </row>
+    <row r="97" spans="1:16" ht="13">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="5"/>
+    </row>
+    <row r="98" spans="1:16" ht="13">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+    </row>
+    <row r="99" spans="1:16" ht="13">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
+    </row>
+    <row r="100" spans="1:16" ht="13">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+    </row>
+    <row r="101" spans="1:16" ht="13">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5"/>
+    </row>
+    <row r="102" spans="1:16" ht="13">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="5"/>
+    </row>
+    <row r="103" spans="1:16" ht="13">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5"/>
+    </row>
+    <row r="104" spans="1:16" ht="13">
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" spans="1:16" ht="13">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+    </row>
+    <row r="106" spans="1:16" ht="13">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="7"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+    </row>
+    <row r="107" spans="1:16" ht="13">
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5"/>
+      <c r="P107" s="5"/>
+    </row>
+    <row r="108" spans="1:16" ht="13">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+    </row>
+    <row r="109" spans="1:16" ht="13">
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SportsCompUpdater/Sports_Comp.xlsx
+++ b/SportsCompUpdater/Sports_Comp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justinlovett/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC43CBF-32BF-D743-9E3F-226C389B0016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE658C7-5928-2D4D-A188-4954E6FBCC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
   <si>
     <t>Player</t>
   </si>
@@ -85,186 +85,12 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Stephen Curry (G) - GSW</t>
-  </si>
-  <si>
-    <t>Joel Embiid (C) - PHI</t>
-  </si>
-  <si>
-    <t>Devin Booker (G) - PHX</t>
-  </si>
-  <si>
-    <t>Jamal Murray (G) - DEN</t>
-  </si>
-  <si>
-    <t>D'Angelo Russell (G) - BKN</t>
-  </si>
-  <si>
-    <t>Miles Bridges (F) - CHA</t>
-  </si>
-  <si>
-    <t>Mitchell Robinson (C) - NYK</t>
-  </si>
-  <si>
-    <t>Trae Young (G) - ATL</t>
-  </si>
-  <si>
-    <t>Ja Morant (G) - MEM</t>
-  </si>
-  <si>
-    <t>Coby White (G) - CHI</t>
-  </si>
-  <si>
-    <t>Shai Gilgeous-Alexander (G) - OKC</t>
-  </si>
-  <si>
-    <t>Darius Garland (G) - CLE</t>
-  </si>
-  <si>
-    <t>Tyler Herro (G) - MIA</t>
-  </si>
-  <si>
     <t>Derrick White</t>
   </si>
   <si>
     <t>Deni Avdija</t>
   </si>
   <si>
-    <t>Jaylen Brown (F/G) - BOS</t>
-  </si>
-  <si>
-    <t>Aaron Gordon (F) - DEN</t>
-  </si>
-  <si>
-    <t>Draymond Green (F) - GSW</t>
-  </si>
-  <si>
-    <t>Karl-Anthony Towns (C) - MIN</t>
-  </si>
-  <si>
-    <t>Domantas Sabonis (F/C) - SAC</t>
-  </si>
-  <si>
-    <t>Brandon Ingram (F) - NOR</t>
-  </si>
-  <si>
-    <t>Jayson Tatum (F/G) - BOS</t>
-  </si>
-  <si>
-    <t>Bam Adebayo (C/F) - MIA</t>
-  </si>
-  <si>
-    <t>Luka Doncic (G/F) - DAL</t>
-  </si>
-  <si>
-    <t>Anthony Edwards (G) - MIN</t>
-  </si>
-  <si>
-    <t>Jalen Green (G) - HOU</t>
-  </si>
-  <si>
-    <t>Evan Mobley (F/C) - CLE</t>
-  </si>
-  <si>
-    <t>James Harden (G) - PHI</t>
-  </si>
-  <si>
-    <t>Myles Turner (C) - IND</t>
-  </si>
-  <si>
-    <t>Jaren Jackson (F/C) - MEM</t>
-  </si>
-  <si>
-    <t>Michael Porter (F) - DEN</t>
-  </si>
-  <si>
-    <t>Lamelo Ball (G) - CHA</t>
-  </si>
-  <si>
-    <t>Onyeka Okongwu (F/C) - ATL</t>
-  </si>
-  <si>
-    <t>Alperen Sengun (C) - HOU</t>
-  </si>
-  <si>
-    <t>Cade Cunningham (G/F) - DET</t>
-  </si>
-  <si>
-    <t>Scottie Barnes (F) - TOR</t>
-  </si>
-  <si>
-    <t>Collin Sexton (G) - UTH</t>
-  </si>
-  <si>
-    <t>Jaden Ivey (G) - DET</t>
-  </si>
-  <si>
-    <t>Bennedict Mathurin (G) - IND</t>
-  </si>
-  <si>
-    <t>Tyrese Maxey (G) - PHI</t>
-  </si>
-  <si>
-    <t>Mark Williams (C) - CHA</t>
-  </si>
-  <si>
-    <t>CJ McCollum (G) - NOR</t>
-  </si>
-  <si>
-    <t>Jabari Smith (F) - HOU</t>
-  </si>
-  <si>
-    <t>Chet Holmgren (F) - OKC</t>
-  </si>
-  <si>
-    <t>Shaedon Sharpe (G) - POR</t>
-  </si>
-  <si>
-    <t>RJ Barrett - (G/F) - TOR</t>
-  </si>
-  <si>
-    <t>Bradley Beal (G) - PHX</t>
-  </si>
-  <si>
-    <t>Pascal Siakam (F) - IND</t>
-  </si>
-  <si>
-    <t>Donovan Mitchell (G) - CLE</t>
-  </si>
-  <si>
-    <t>Mikal Bridges (F) - BKN</t>
-  </si>
-  <si>
-    <t>Brandon Miller (F) - CHA</t>
-  </si>
-  <si>
-    <t>De'Aaaron Fox (G) - SAS</t>
-  </si>
-  <si>
-    <t>Zach Lavine (G) - SAC</t>
-  </si>
-  <si>
-    <t>Buddy Hield (G) - GSW</t>
-  </si>
-  <si>
-    <t>Jalen Brunson (G) - NYC</t>
-  </si>
-  <si>
-    <t>Amen Thompson (F) - HOU</t>
-  </si>
-  <si>
-    <t>Ausar Thompson (F) - DET</t>
-  </si>
-  <si>
-    <t>Julius Randle (F/C) - MIN</t>
-  </si>
-  <si>
-    <t>Andrew Wiggins (F/G) - MIA</t>
-  </si>
-  <si>
-    <t>Josh Giddey (G/F) - CHI</t>
-  </si>
-  <si>
     <t>Stephon Castle</t>
   </si>
   <si>
@@ -277,9 +103,6 @@
     <t>2025-26</t>
   </si>
   <si>
-    <t>Andre Drummond (C) - PHI</t>
-  </si>
-  <si>
     <t>Cam Thomas</t>
   </si>
   <si>
@@ -313,7 +136,181 @@
     <t>Ace Bailey</t>
   </si>
   <si>
-    <t>Kon Knueppel</t>
+    <t>De'Aaron Fox</t>
+  </si>
+  <si>
+    <t>Stephen Curry</t>
+  </si>
+  <si>
+    <t>Zach Lavine</t>
+  </si>
+  <si>
+    <t>Jaylen Brown</t>
+  </si>
+  <si>
+    <t>Aaron Gordon</t>
+  </si>
+  <si>
+    <t>Andre Drummond</t>
+  </si>
+  <si>
+    <t>D'Angelo Russell</t>
+  </si>
+  <si>
+    <t>Draymond Green</t>
+  </si>
+  <si>
+    <t>Karl-Anthony Towns</t>
+  </si>
+  <si>
+    <t>Domantas Sabonis</t>
+  </si>
+  <si>
+    <t>Buddy Hield</t>
+  </si>
+  <si>
+    <t>Brandon Ingram</t>
+  </si>
+  <si>
+    <t>Jayson Tatum</t>
+  </si>
+  <si>
+    <t>Bam Adebayo</t>
+  </si>
+  <si>
+    <t>Mitchell Robinson</t>
+  </si>
+  <si>
+    <t>Collin Sexton</t>
+  </si>
+  <si>
+    <t>Luka Doncic</t>
+  </si>
+  <si>
+    <t>Miles Bridges</t>
+  </si>
+  <si>
+    <t>Coby White</t>
+  </si>
+  <si>
+    <t>Ja Morant</t>
+  </si>
+  <si>
+    <t>Anthony Edwards</t>
+  </si>
+  <si>
+    <t>Jalen Green</t>
+  </si>
+  <si>
+    <t>Evan Mobley</t>
+  </si>
+  <si>
+    <t>Jaden Ivey</t>
+  </si>
+  <si>
+    <t>Bennedict Mathurin</t>
+  </si>
+  <si>
+    <t>Mark Williams</t>
+  </si>
+  <si>
+    <t>Tyrese Maxey</t>
+  </si>
+  <si>
+    <t>Jalen Brunson</t>
+  </si>
+  <si>
+    <t>Amen Thompson</t>
+  </si>
+  <si>
+    <t>Ausar Thompson</t>
+  </si>
+  <si>
+    <t>Devin Booker</t>
+  </si>
+  <si>
+    <t>RJ Barrett</t>
+  </si>
+  <si>
+    <t>James Harden</t>
+  </si>
+  <si>
+    <t>Bradley Beal</t>
+  </si>
+  <si>
+    <t>CJ McCollum</t>
+  </si>
+  <si>
+    <t>Joel Embiid</t>
+  </si>
+  <si>
+    <t>Julius Randle</t>
+  </si>
+  <si>
+    <t>Andrew Wiggins</t>
+  </si>
+  <si>
+    <t>Myles Turner</t>
+  </si>
+  <si>
+    <t>Pascal Siakam</t>
+  </si>
+  <si>
+    <t>Jamal Murray</t>
+  </si>
+  <si>
+    <t>Donovan Mitchell</t>
+  </si>
+  <si>
+    <t>Mikal Bridges</t>
+  </si>
+  <si>
+    <t>Shai Gilgeous-Alexander</t>
+  </si>
+  <si>
+    <t>Trae Young</t>
+  </si>
+  <si>
+    <t>Jaren Jackson</t>
+  </si>
+  <si>
+    <t>Michael Porter</t>
+  </si>
+  <si>
+    <t>Darius Garland</t>
+  </si>
+  <si>
+    <t>Tyler Herro</t>
+  </si>
+  <si>
+    <t>Lamelo Ball</t>
+  </si>
+  <si>
+    <t>Onyeka Okongwu</t>
+  </si>
+  <si>
+    <t>Alperen Sengun</t>
+  </si>
+  <si>
+    <t>Josh Giddey</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>Scottie Barnes</t>
+  </si>
+  <si>
+    <t>Jabari Smith</t>
+  </si>
+  <si>
+    <t>Chet Holmgren</t>
+  </si>
+  <si>
+    <t>Shaedon Sharpe</t>
+  </si>
+  <si>
+    <t>Brandon Miller</t>
   </si>
 </sst>
 </file>
@@ -331,31 +328,37 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Verdana"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Verdana"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -365,6 +368,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -377,11 +381,13 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -434,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -506,6 +512,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,7 +898,7 @@
     </row>
     <row r="2" spans="1:16" ht="13">
       <c r="A2" s="4" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -911,7 +918,7 @@
     </row>
     <row r="3" spans="1:16" ht="14">
       <c r="A3" s="27" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -961,7 +968,7 @@
     </row>
     <row r="4" spans="1:16" ht="14">
       <c r="A4" s="27" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1001,7 +1008,7 @@
     </row>
     <row r="5" spans="1:16" ht="14">
       <c r="A5" s="27" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1041,7 +1048,7 @@
     </row>
     <row r="6" spans="1:16" ht="14">
       <c r="A6" s="27" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1091,7 +1098,7 @@
     </row>
     <row r="7" spans="1:16" ht="14">
       <c r="A7" s="27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1111,7 +1118,7 @@
     </row>
     <row r="8" spans="1:16" ht="14">
       <c r="A8" s="27" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1131,7 +1138,7 @@
     </row>
     <row r="9" spans="1:16" ht="14">
       <c r="A9" s="27" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1151,7 +1158,7 @@
     </row>
     <row r="10" spans="1:16" ht="14">
       <c r="A10" s="27" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1171,7 +1178,7 @@
     </row>
     <row r="11" spans="1:16" ht="14">
       <c r="A11" s="27" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1191,7 +1198,7 @@
     </row>
     <row r="12" spans="1:16" ht="14">
       <c r="A12" s="27" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1211,7 +1218,7 @@
     </row>
     <row r="13" spans="1:16" ht="14">
       <c r="A13" s="27" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1231,7 +1238,7 @@
     </row>
     <row r="14" spans="1:16" ht="14">
       <c r="A14" s="27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1251,7 +1258,7 @@
     </row>
     <row r="15" spans="1:16" ht="14">
       <c r="A15" s="27" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1271,7 +1278,7 @@
     </row>
     <row r="16" spans="1:16" ht="14">
       <c r="A16" s="27" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1291,7 +1298,7 @@
     </row>
     <row r="17" spans="1:16" ht="14">
       <c r="A17" s="27" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1311,7 +1318,7 @@
     </row>
     <row r="18" spans="1:16" ht="14">
       <c r="A18" s="27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1331,7 +1338,7 @@
     </row>
     <row r="19" spans="1:16" ht="14">
       <c r="A19" s="27" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1351,7 +1358,7 @@
     </row>
     <row r="20" spans="1:16" ht="14">
       <c r="A20" s="27" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1371,7 +1378,7 @@
     </row>
     <row r="21" spans="1:16" ht="14">
       <c r="A21" s="27" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1391,7 +1398,7 @@
     </row>
     <row r="22" spans="1:16" ht="14">
       <c r="A22" s="27" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1410,8 +1417,8 @@
       <c r="P22" s="16"/>
     </row>
     <row r="23" spans="1:16" ht="13">
-      <c r="A23" s="26" t="s">
-        <v>41</v>
+      <c r="A23" s="33" t="s">
+        <v>54</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
@@ -1430,8 +1437,8 @@
       <c r="P23" s="26"/>
     </row>
     <row r="24" spans="1:16" ht="13">
-      <c r="A24" s="26" t="s">
-        <v>42</v>
+      <c r="A24" s="33" t="s">
+        <v>55</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -1450,8 +1457,8 @@
       <c r="P24" s="26"/>
     </row>
     <row r="25" spans="1:16" ht="13">
-      <c r="A25" s="26" t="s">
-        <v>43</v>
+      <c r="A25" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
@@ -1470,8 +1477,8 @@
       <c r="P25" s="26"/>
     </row>
     <row r="26" spans="1:16" ht="13">
-      <c r="A26" s="26" t="s">
-        <v>54</v>
+      <c r="A26" s="33" t="s">
+        <v>57</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -1490,8 +1497,8 @@
       <c r="P26" s="26"/>
     </row>
     <row r="27" spans="1:16" ht="13">
-      <c r="A27" s="26" t="s">
-        <v>55</v>
+      <c r="A27" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -1510,8 +1517,8 @@
       <c r="P27" s="26"/>
     </row>
     <row r="28" spans="1:16" ht="13">
-      <c r="A28" s="26" t="s">
-        <v>56</v>
+      <c r="A28" s="33" t="s">
+        <v>60</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -1530,8 +1537,8 @@
       <c r="P28" s="26"/>
     </row>
     <row r="29" spans="1:16" ht="13">
-      <c r="A29" s="26" t="s">
-        <v>57</v>
+      <c r="A29" s="33" t="s">
+        <v>59</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -1550,8 +1557,8 @@
       <c r="P29" s="26"/>
     </row>
     <row r="30" spans="1:16" ht="13">
-      <c r="A30" s="26" t="s">
-        <v>71</v>
+      <c r="A30" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
@@ -1570,8 +1577,8 @@
       <c r="P30" s="26"/>
     </row>
     <row r="31" spans="1:16" ht="13">
-      <c r="A31" s="26" t="s">
-        <v>72</v>
+      <c r="A31" s="33" t="s">
+        <v>62</v>
       </c>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
@@ -1590,8 +1597,8 @@
       <c r="P31" s="26"/>
     </row>
     <row r="32" spans="1:16" ht="13">
-      <c r="A32" s="26" t="s">
-        <v>73</v>
+      <c r="A32" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
@@ -1611,7 +1618,7 @@
     </row>
     <row r="33" spans="1:16" ht="13">
       <c r="A33" s="26" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -1631,7 +1638,7 @@
     </row>
     <row r="34" spans="1:16" ht="13">
       <c r="A34" s="26" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="26"/>
@@ -1651,7 +1658,7 @@
     </row>
     <row r="35" spans="1:16" ht="13">
       <c r="A35" s="26" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -1671,7 +1678,7 @@
     </row>
     <row r="36" spans="1:16" ht="13">
       <c r="A36" s="26" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -1691,7 +1698,7 @@
     </row>
     <row r="37" spans="1:16" ht="13">
       <c r="A37" s="26" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -1711,7 +1718,7 @@
     </row>
     <row r="38" spans="1:16" ht="13">
       <c r="A38" s="26" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="B38" s="26"/>
       <c r="C38" s="26"/>
@@ -1731,7 +1738,7 @@
     </row>
     <row r="39" spans="1:16" ht="13">
       <c r="A39" s="26" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
@@ -1751,7 +1758,7 @@
     </row>
     <row r="40" spans="1:16" ht="13">
       <c r="A40" s="26" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
@@ -1883,7 +1890,7 @@
     </row>
     <row r="44" spans="1:16" ht="14">
       <c r="A44" s="27" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1901,7 +1908,7 @@
     </row>
     <row r="45" spans="1:16" ht="14">
       <c r="A45" s="27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -1918,7 +1925,7 @@
     </row>
     <row r="46" spans="1:16" ht="14">
       <c r="A46" s="27" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -1937,7 +1944,7 @@
     </row>
     <row r="47" spans="1:16" ht="14">
       <c r="A47" s="27" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -1956,7 +1963,7 @@
     </row>
     <row r="48" spans="1:16" ht="14">
       <c r="A48" s="27" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -1975,7 +1982,7 @@
     </row>
     <row r="49" spans="1:16" ht="14">
       <c r="A49" s="27" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -1994,7 +2001,7 @@
     </row>
     <row r="50" spans="1:16" ht="14">
       <c r="A50" s="27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2013,7 +2020,7 @@
     </row>
     <row r="51" spans="1:16" ht="14">
       <c r="A51" s="27" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2032,7 +2039,7 @@
     </row>
     <row r="52" spans="1:16" ht="14">
       <c r="A52" s="27" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2052,7 +2059,7 @@
     </row>
     <row r="53" spans="1:16" ht="14">
       <c r="A53" s="27" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2071,7 +2078,7 @@
     </row>
     <row r="54" spans="1:16" ht="14">
       <c r="A54" s="27" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2090,7 +2097,7 @@
     </row>
     <row r="55" spans="1:16" ht="14">
       <c r="A55" s="27" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2109,7 +2116,7 @@
     </row>
     <row r="56" spans="1:16" ht="14">
       <c r="A56" s="27" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2128,7 +2135,7 @@
     </row>
     <row r="57" spans="1:16" ht="14">
       <c r="A57" s="27" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2148,7 +2155,7 @@
     </row>
     <row r="58" spans="1:16" ht="14">
       <c r="A58" s="27" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2167,7 +2174,7 @@
     </row>
     <row r="59" spans="1:16" ht="14">
       <c r="A59" s="27" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2186,7 +2193,7 @@
     </row>
     <row r="60" spans="1:16" ht="14">
       <c r="A60" s="27" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2206,7 +2213,7 @@
     </row>
     <row r="61" spans="1:16" ht="14">
       <c r="A61" s="27" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2226,7 +2233,7 @@
     </row>
     <row r="62" spans="1:16" ht="14">
       <c r="A62" s="27" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2245,8 +2252,8 @@
       <c r="P62" s="16"/>
     </row>
     <row r="63" spans="1:16" ht="13">
-      <c r="A63" s="26" t="s">
-        <v>48</v>
+      <c r="A63" s="33" t="s">
+        <v>83</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2264,8 +2271,8 @@
       <c r="P63" s="26"/>
     </row>
     <row r="64" spans="1:16" ht="13">
-      <c r="A64" s="26" t="s">
-        <v>49</v>
+      <c r="A64" s="33" t="s">
+        <v>84</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2283,8 +2290,8 @@
       <c r="P64" s="26"/>
     </row>
     <row r="65" spans="1:16" ht="13">
-      <c r="A65" s="26" t="s">
-        <v>50</v>
+      <c r="A65" s="33" t="s">
+        <v>85</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2302,8 +2309,8 @@
       <c r="P65" s="26"/>
     </row>
     <row r="66" spans="1:16" ht="13">
-      <c r="A66" s="26" t="s">
-        <v>76</v>
+      <c r="A66" s="33" t="s">
+        <v>86</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2322,8 +2329,8 @@
       <c r="P66" s="26"/>
     </row>
     <row r="67" spans="1:16" ht="13">
-      <c r="A67" s="26" t="s">
-        <v>51</v>
+      <c r="A67" s="33" t="s">
+        <v>87</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2341,8 +2348,8 @@
       <c r="P67" s="26"/>
     </row>
     <row r="68" spans="1:16" ht="13">
-      <c r="A68" s="26" t="s">
-        <v>52</v>
+      <c r="A68" s="33" t="s">
+        <v>88</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2360,8 +2367,8 @@
       <c r="P68" s="26"/>
     </row>
     <row r="69" spans="1:16" ht="13">
-      <c r="A69" s="26" t="s">
-        <v>59</v>
+      <c r="A69" s="33" t="s">
+        <v>89</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2379,8 +2386,8 @@
       <c r="P69" s="26"/>
     </row>
     <row r="70" spans="1:16" ht="13">
-      <c r="A70" s="26" t="s">
-        <v>60</v>
+      <c r="A70" s="33" t="s">
+        <v>90</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2399,8 +2406,8 @@
       <c r="P70" s="26"/>
     </row>
     <row r="71" spans="1:16" ht="13">
-      <c r="A71" s="26" t="s">
-        <v>61</v>
+      <c r="A71" s="33" t="s">
+        <v>91</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2418,8 +2425,8 @@
       <c r="P71" s="26"/>
     </row>
     <row r="72" spans="1:16" ht="13">
-      <c r="A72" s="26" t="s">
-        <v>67</v>
+      <c r="A72" s="33" t="s">
+        <v>92</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2438,7 +2445,7 @@
     </row>
     <row r="73" spans="1:16" ht="13">
       <c r="A73" s="26" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2457,7 +2464,7 @@
     </row>
     <row r="74" spans="1:16" ht="13">
       <c r="A74" s="26" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2476,7 +2483,7 @@
     </row>
     <row r="75" spans="1:16" ht="13">
       <c r="A75" s="26" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2495,7 +2502,7 @@
     </row>
     <row r="76" spans="1:16" ht="13">
       <c r="A76" s="26" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2514,7 +2521,7 @@
     </row>
     <row r="77" spans="1:16" ht="13">
       <c r="A77" s="26" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2533,7 +2540,7 @@
     </row>
     <row r="78" spans="1:16" ht="13">
       <c r="A78" s="26" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2552,7 +2559,7 @@
     </row>
     <row r="79" spans="1:16" ht="13">
       <c r="A79" s="26" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2571,7 +2578,7 @@
     </row>
     <row r="80" spans="1:16" ht="13">
       <c r="A80" s="26" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2589,9 +2596,7 @@
       <c r="P80" s="26"/>
     </row>
     <row r="81" spans="1:16" ht="13">
-      <c r="A81" s="26" t="s">
-        <v>93</v>
-      </c>
+      <c r="A81" s="26"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
